--- a/artfynd/A 48330-2025 artfynd.xlsx
+++ b/artfynd/A 48330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129494074</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48330-2025 artfynd.xlsx
+++ b/artfynd/A 48330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129494074</v>
       </c>
       <c r="B2" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48330-2025 artfynd.xlsx
+++ b/artfynd/A 48330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129494074</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48330-2025 artfynd.xlsx
+++ b/artfynd/A 48330-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129494074</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
